--- a/outputs/PRD-2.0_capa_management/test_library_v1.0.xlsx
+++ b/outputs/PRD-2.0_capa_management/test_library_v1.0.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,13 +67,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +493,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>27 test cases drafted, 15 requirement gaps raised, 1 criteria without a test case</t>
+          <t>27 test cases drafted, 15 requirement gaps raised, 1 criteria without a test case, 5 tested on an assumption</t>
         </is>
       </c>
     </row>
@@ -2374,62 +2382,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CAPA-202</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Due dates must be reasonable.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>TC-202-03, TC-202-05</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>vague_term</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>assumed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>CAPA-202</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>The assignee should receive a notification.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>TC-202-01</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>weak_modal</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>assumed</t>
         </is>
       </c>
     </row>
@@ -2460,32 +2468,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>CAPA-203</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Escalations happen quickly.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>TC-203-01, TC-203-03</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>vague_term</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>assumed</t>
         </is>
       </c>
     </row>
@@ -2568,32 +2576,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>CAPA-205</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>The owner can edit any field of a closed CAPA.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>TC-205-01, TC-205-02, TC-205-03, TC-205-04</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>gxp_control_missing</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>assumed</t>
         </is>
       </c>
     </row>
@@ -2624,56 +2632,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>CAPA-206</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Results are approved.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>TC-206-01, TC-206-02, TC-206-04</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>missing_actor</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>assumed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CAPA-206</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>TBD: what happens if the CAPA was not effective.</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
